--- a/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IIJIY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>IIJIY</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2172200</v>
+      </c>
+      <c r="E8" s="3">
         <v>2115800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1825300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1901000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1863900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1925900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1900300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1736600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1657600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1063500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1033800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1049600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1046700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>965800</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1693200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1659000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1403000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1465400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1438700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1561700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1597400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1475100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1391800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>893300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>852500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>861300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>853800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>767100</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>479000</v>
+      </c>
+      <c r="E10" s="3">
         <v>456800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>422200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>435600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>425100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>364200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>302900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>261500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>265800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>170200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>181200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>188300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>193000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>198600</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E12" s="3">
         <v>4300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3700</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,83 +979,89 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-23400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-9000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E15" s="3">
         <v>24300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>23200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>25700</v>
       </c>
       <c r="H15" s="3">
         <v>25700</v>
       </c>
       <c r="I15" s="3">
+        <v>25700</v>
+      </c>
+      <c r="J15" s="3">
         <v>26400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>84900</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>10</v>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1953000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1914600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1633000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1697600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1668800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1792100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1819900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1679500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1594000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1029100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>988700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1006600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>994300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>895500</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>219200</v>
+      </c>
+      <c r="E18" s="3">
         <v>201200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>192300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>203400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>195000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>133800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>80400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>57100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>63700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>45000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>43000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>52400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>70300</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,8 +1211,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1188,224 +1221,239 @@
         <v>2600</v>
       </c>
       <c r="E20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>16200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2800</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>241000</v>
+      </c>
+      <c r="E21" s="3">
         <v>222900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>214400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>227800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>204500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>157700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>99400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>66100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>151900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>112400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>119500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>129400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>141000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>141500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E22" s="3">
         <v>6600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>3700</v>
       </c>
       <c r="F22" s="3">
         <v>3700</v>
       </c>
       <c r="G22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H22" s="3">
         <v>4200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2600</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>221600</v>
+      </c>
+      <c r="E23" s="3">
         <v>194900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>191300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>205400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>199000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>126900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>66500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>52700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>75100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>36600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>45500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>43800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>57500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>70500</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E24" s="3">
         <v>60600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>59200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>62700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>68900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>38300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>27600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>19300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>25400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>16000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>16200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23700</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>153500</v>
+      </c>
+      <c r="E26" s="3">
         <v>134300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>132100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>142800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>130100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>88600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>39000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>33400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>49700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>29500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>27700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>41000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>46800</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>152100</v>
+      </c>
+      <c r="E27" s="3">
         <v>133100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>131100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>141700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>129100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>87800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>37200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>31800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>48100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>29700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>28300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>41000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>48200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1673,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>10</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>10</v>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,9 +1784,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1728,89 +1797,95 @@
         <v>-2600</v>
       </c>
       <c r="E32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-16200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>152100</v>
+      </c>
+      <c r="E33" s="3">
         <v>133100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>131100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>141700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>129100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>87800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>37200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>31800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>48100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>29700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>28300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>41000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>48200</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>152100</v>
+      </c>
+      <c r="E35" s="3">
         <v>133100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>131100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>141700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>129100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>87800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>37200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>31800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>48100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>29700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>28300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>41000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>48200</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>241500</v>
+      </c>
+      <c r="E41" s="3">
         <v>217300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>300600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>319500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>390300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>384000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>359400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>288400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>201500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>148000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>143800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>179900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>205400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>111400</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2061,8 +2150,8 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>10</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>10</v>
@@ -2076,324 +2165,348 @@
       <c r="P42" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>390500</v>
+      </c>
+      <c r="E43" s="3">
         <v>376400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>302000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>311000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>310000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>314600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>306500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>301200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>299700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>184500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>174400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>189800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>176000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>170500</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E44" s="3">
         <v>31300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>21300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>21500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>19600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>30700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>18900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>14700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>15300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>11800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E45" s="3">
         <v>56700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>35800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>32600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>27100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>30500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>78200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>59600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>64100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>76900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>46600</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>957000</v>
+      </c>
+      <c r="E46" s="3">
         <v>869400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>792600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>802500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>860400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>844500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>804700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>712700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>632600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>429500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>392500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>444300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>473600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>340300</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>482900</v>
+      </c>
+      <c r="E47" s="3">
         <v>475000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>360600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>322300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>317200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>329100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>249700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>271700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>156500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>21400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>21000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>18500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>14600</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>529700</v>
+      </c>
+      <c r="E48" s="3">
         <v>531100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>464900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>526500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>516500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>613000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>631600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>299000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>300000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>268100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>252300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>250500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>247100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>209300</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>210200</v>
+      </c>
+      <c r="E49" s="3">
         <v>209200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>189600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>199200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>213300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>208300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>226400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>224700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>219800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>62400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>71400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>86200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>94400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>97800</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,9 +2597,12 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2496,8 +2615,8 @@
       <c r="F52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
@@ -2509,26 +2628,29 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>119700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>145300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>128400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>125100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>117800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>84300</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2181900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2086400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1809600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1852000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1908900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1996200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1919300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1509700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1444800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>926000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>866100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>927300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>951400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>746400</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,188 +2784,201 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E57" s="3">
         <v>201900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>168200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>167900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>170800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>174000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>170000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>198200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>140800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>98800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>102200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>103900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>105300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>99700</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>223700</v>
+      </c>
+      <c r="E58" s="3">
         <v>224500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>199200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>126600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>134800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>167800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>144800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>173900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>140400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>94800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>97100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>108900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>129500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>126500</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>374200</v>
+      </c>
+      <c r="E59" s="3">
         <v>330300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>282900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>291300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>326600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>320600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>295700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>105300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>86400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>75900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>65800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>74900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>62700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>68100</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>814700</v>
+      </c>
+      <c r="E60" s="3">
         <v>756700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>650300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>585700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>632300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>662400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>610500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>477400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>396800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>269500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>265100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>287800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>297400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>294400</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2844,89 +2986,95 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>27100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>45300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>63300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>113100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>230200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>248800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>127300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>57200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>37000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>42200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>57700</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>349600</v>
+      </c>
+      <c r="E62" s="3">
         <v>338600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>276400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>303200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>328400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>408300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>413500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>70800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>75100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>63500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>66400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>60600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>52200</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1179000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1137600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>969800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>954500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1047400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1173700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1175300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>813700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>748200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>476200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>389500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>394100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>402600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>404500</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>617400</v>
+      </c>
+      <c r="E72" s="3">
         <v>533500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>433800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>384200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>304900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>226500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>153300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>111300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>79100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>30400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-26300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-58200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>993700</v>
+      </c>
+      <c r="E76" s="3">
         <v>939500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>831400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>888500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>852500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>813400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>734900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>688300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>689900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>449800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>476600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>533200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>548800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>341800</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>152100</v>
+      </c>
+      <c r="E81" s="3">
         <v>133100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>131100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>141700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>129100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>87800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>37200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>31800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>48100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>29700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>28300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>41000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>48200</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>205500</v>
+      </c>
+      <c r="E83" s="3">
         <v>209500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>193700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>216700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>234200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>252900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>265100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>141000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>81500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>73400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>72900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>82500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>80800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>68200</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>317300</v>
+      </c>
+      <c r="E89" s="3">
         <v>190500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>269600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>289800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>358800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>366600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>310300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>227000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>124900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>49700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>88600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>110100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>80500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>88700</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-79500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-77600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-88700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-55900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-57800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-66900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-63900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-148500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-71600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-80100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-69600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-83600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-50800</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-165600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-145200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-118500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-138300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-97500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-119500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-67500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-78400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-122800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-49700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-61600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-68900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-93500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E96" s="3">
         <v>41000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>37600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>36900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>31600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>13900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>11300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>11000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>11500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-7600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-7400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-8600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-8300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-120200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-131300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-137500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-193600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-224800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-213500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-179900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-53100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>16800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-38200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-53600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>104300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-45400</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-86400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-37000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>40500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>34300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>62400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>96000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>93100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
